--- a/django/camac/statistics/config/kt_ag/dossiers_service-afb.xlsx
+++ b/django/camac/statistics/config/kt_ag/dossiers_service-afb.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0578BF0D-7ED9-424D-A1FC-2B96F4CD8B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0353095-DDBF-48F9-AC27-E2412DC0E425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="31755" windowHeight="16770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="20565" tabRatio="887" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="36" r:id="rId8"/>
+    <pivotCache cacheId="43" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="34">
   <si>
     <t>Dossier-Nr.</t>
   </si>
@@ -80,9 +80,6 @@
     <t>Dauer</t>
   </si>
   <si>
-    <t>Anzahl</t>
-  </si>
-  <si>
     <t>&lt;= 30 Tage</t>
   </si>
   <si>
@@ -98,32 +95,62 @@
     <t>Pivot-Tabelle per Rechtsklick -&gt; "Aktualisieren" neu laden</t>
   </si>
   <si>
-    <t>Anzahl von Dossier-Nr.</t>
-  </si>
-  <si>
-    <t>Spaltenbeschriftungen</t>
-  </si>
-  <si>
-    <t>Zeilenbeschriftungen</t>
-  </si>
-  <si>
     <t>(Leer)</t>
   </si>
   <si>
     <t>Gesamtergebnis</t>
   </si>
   <si>
-    <t>Mittelwert von Durchlaufzeit</t>
-  </si>
-  <si>
     <t>Anteil</t>
+  </si>
+  <si>
+    <t>Anzahl Dossiers</t>
+  </si>
+  <si>
+    <t>Zuständige Person</t>
+  </si>
+  <si>
+    <t>Total Anzahl Dossiers</t>
+  </si>
+  <si>
+    <t>Anzahl Dossier pro Zuständige Person</t>
+  </si>
+  <si>
+    <t>Mittelwert von Durchlaufzeit in Tage</t>
+  </si>
+  <si>
+    <t>Durchschnittliche Durchlaufzeit Dossiers pro Zuständige Person</t>
+  </si>
+  <si>
+    <t>Dossiertyp</t>
+  </si>
+  <si>
+    <t>Die Dossiertypen mit "-Migration" stammen aus dem alten System.</t>
+  </si>
+  <si>
+    <t>Anzahl Dossiers nach Dossiertyp pro Zuständige Person</t>
+  </si>
+  <si>
+    <t>Anzahl fristgerechte erledigte Dossiers pro Zuständige Person</t>
+  </si>
+  <si>
+    <t>Frist erreicht</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Anteil Dossiers</t>
+  </si>
+  <si>
+    <t>Anzhal Gesuche nach Dossiertyp pro Gemeinde</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -233,6 +260,12 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="9">
@@ -381,7 +414,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -396,14 +429,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="21">
     <cellStyle name="Accent" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
@@ -428,24 +462,18 @@
     <cellStyle name="Text" xfId="19" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
     <cellStyle name="Warning" xfId="20" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="4">
     <dxf>
-      <alignment horizontal="right"/>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="right"/>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="right"/>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="right"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right"/>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -461,7 +489,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Stoppe Tilo  Extern" refreshedDate="46111.666776851853" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="20" xr:uid="{00000000-000A-0000-FFFF-FFFF50000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Stoppe Tilo  Extern" refreshedDate="46121.734699884262" missingItemsLimit="0" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="20" xr:uid="{00000000-000A-0000-FFFF-FFFF50000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:J1048576" sheet="Data"/>
   </cacheSource>
@@ -470,14 +498,8 @@
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
     <cacheField name="Gesuchstyp" numFmtId="0">
-      <sharedItems containsNonDate="0" containsBlank="1" count="7">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1" count="1">
         <m/>
-        <s v="Baugesuch" u="1"/>
-        <s v="Anfrage" u="1"/>
-        <s v="PGV" u="1"/>
-        <s v="Baugesuch mit UVP" u="1"/>
-        <s v="Anfrage intern" u="1"/>
-        <s v="Baugesuch Migration" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Parzellen" numFmtId="0">
@@ -487,31 +509,13 @@
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
     <cacheField name="Zuständig" numFmtId="0">
-      <sharedItems containsNonDate="0" containsBlank="1" count="12">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1" count="1">
         <m/>
-        <s v="Max Mustermann" u="1"/>
-        <s v="Peter Müller" u="1"/>
-        <s v="Peter" u="1"/>
-        <s v="Jochen" u="1"/>
-        <s v="Gerd" u="1"/>
-        <s v="S. Schmidt" u="1"/>
-        <s v="M. Müller" u="1"/>
-        <s v="B. Brunner" u="1"/>
-        <s v="K. Keller" u="1"/>
-        <s v="W. Weber" u="1"/>
-        <s v="F. Fischer" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Gemeinde" numFmtId="0">
-      <sharedItems containsNonDate="0" containsBlank="1" count="8">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1" count="1">
         <m/>
-        <s v="Aarburg" u="1"/>
-        <s v="Abtwil" u="1"/>
-        <s v="Baden" u="1"/>
-        <s v="Brugg" u="1"/>
-        <s v="Lenzburg" u="1"/>
-        <s v="Zofingen" u="1"/>
-        <s v="Dietwil" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Durchlaufzeit" numFmtId="0">
@@ -524,10 +528,8 @@
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
     <cacheField name="Fristgerecht" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="1" count="3">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1" count="1">
         <m/>
-        <n v="1" u="1"/>
-        <n v="0" u="1"/>
       </sharedItems>
     </cacheField>
   </cacheFields>
@@ -785,7 +787,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000001000000}" name="PivotTable3" cacheId="36" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000001000000}" name="PivotTable3" cacheId="43" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" grandTotalCaption="Total Anzahl Dossiers" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person">
   <location ref="A3:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField dataField="1" showAll="0"/>
@@ -793,19 +795,8 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item m="1" x="8"/>
-        <item m="1" x="11"/>
-        <item m="1" x="9"/>
-        <item m="1" x="7"/>
-        <item m="1" x="6"/>
-        <item m="1" x="10"/>
+      <items count="2">
         <item x="0"/>
-        <item m="1" x="3"/>
-        <item m="1" x="4"/>
-        <item m="1" x="5"/>
-        <item m="1" x="1"/>
-        <item m="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -820,7 +811,7 @@
   </rowFields>
   <rowItems count="2">
     <i>
-      <x v="6"/>
+      <x/>
     </i>
     <i t="grand">
       <x/>
@@ -830,7 +821,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Anzahl" fld="0" subtotal="count" baseField="4" baseItem="0"/>
+    <dataField name="Anzahl Dossiers" fld="0" subtotal="count" baseField="4" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -842,7 +833,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0400-000002000000}" name="PivotTable1" cacheId="36" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0400-000002000000}" name="PivotTable1" cacheId="43" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person">
   <location ref="A3:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -850,19 +841,8 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item m="1" x="8"/>
-        <item m="1" x="11"/>
-        <item m="1" x="9"/>
-        <item m="1" x="7"/>
-        <item m="1" x="6"/>
-        <item m="1" x="10"/>
+      <items count="2">
         <item x="0"/>
-        <item m="1" x="3"/>
-        <item m="1" x="4"/>
-        <item m="1" x="5"/>
-        <item m="1" x="1"/>
-        <item m="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -877,7 +857,7 @@
   </rowFields>
   <rowItems count="2">
     <i>
-      <x v="6"/>
+      <x/>
     </i>
     <i t="grand">
       <x/>
@@ -887,116 +867,21 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Mittelwert von Durchlaufzeit" fld="6" subtotal="average" baseField="0" baseItem="0" numFmtId="2"/>
+    <dataField name="Mittelwert von Durchlaufzeit in Tage" fld="6" subtotal="average" baseField="0" baseItem="0" numFmtId="1"/>
   </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-000003000000}" name="PivotTable2" cacheId="36" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:C7" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item m="1" x="8"/>
-        <item m="1" x="11"/>
-        <item m="1" x="9"/>
-        <item m="1" x="7"/>
-        <item m="1" x="6"/>
-        <item m="1" x="10"/>
-        <item x="0"/>
-        <item m="1" x="3"/>
-        <item m="1" x="4"/>
-        <item m="1" x="5"/>
-        <item m="1" x="1"/>
-        <item m="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="4">
-        <item n="Nein" m="1" x="2"/>
-        <item n="Ja" m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="6"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="2">
-    <field x="9"/>
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="2"/>
-      <x/>
-    </i>
-    <i r="1" i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Anzahl" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Anteil" fld="0" subtotal="count" showDataAs="percentOfRow" baseField="0" baseItem="0" numFmtId="10"/>
-  </dataFields>
-  <formats count="3">
-    <format dxfId="5">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+  <formats count="2">
+    <format dxfId="3">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
-          <reference field="9" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
+          <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="4">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="2">
+    <format dxfId="2">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
             <x v="0"/>
-            <x v="1"/>
-          </reference>
-          <reference field="9" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="3">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-          <reference field="9" count="1" selected="0">
-            <x v="1"/>
           </reference>
         </references>
       </pivotArea>
@@ -1011,54 +896,155 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0600-000004000000}" name="PivotTable4" cacheId="36" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:C6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B456AD4D-9646-4CC1-84EE-A09565AD0DDF}" name="PivotTable1" cacheId="43" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Frist erreicht">
+  <location ref="G3:H6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField dataField="1" showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="8">
-        <item m="1" x="2"/>
-        <item m="1" x="5"/>
-        <item m="1" x="1"/>
-        <item m="1" x="6"/>
-        <item m="1" x="4"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
         <item x="0"/>
-        <item m="1" x="3"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item m="1" x="8"/>
-        <item m="1" x="11"/>
-        <item m="1" x="9"/>
-        <item m="1" x="7"/>
-        <item m="1" x="6"/>
-        <item m="1" x="10"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0" sortType="ascending">
+      <items count="2">
         <item x="0"/>
-        <item m="1" x="3"/>
-        <item m="1" x="4"/>
-        <item m="1" x="5"/>
-        <item m="1" x="1"/>
-        <item m="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="4"/>
   </rowFields>
   <rowItems count="2">
     <i>
-      <x v="6"/>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="9"/>
+  </colFields>
+  <colItems count="1">
+    <i>
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Anteil Dossiers" fld="0" subtotal="count" showDataAs="percentOfRow" baseField="4" baseItem="0" numFmtId="10"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-000003000000}" name="PivotTable2" cacheId="43" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" grandTotalCaption="Total" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Frist erreicht">
+  <location ref="A3:C6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" multipleItemSelectionAllowed="1" showAll="0" includeNewItemsInFilter="1" sortType="ascending">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="9"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Anzahl Dossiers" fld="0" subtotal="count" baseField="4" baseItem="1"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0600-000004000000}" name="PivotTable4" cacheId="43" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Dossiertyp">
+  <location ref="A3:C6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x/>
     </i>
     <i t="grand">
       <x/>
@@ -1069,14 +1055,14 @@
   </colFields>
   <colItems count="2">
     <i>
-      <x v="5"/>
+      <x/>
     </i>
     <i t="grand">
       <x/>
     </i>
   </colItems>
   <dataFields count="1">
-    <dataField name="Anzahl von Dossier-Nr." fld="0" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Anzahl Dossiers" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -1087,20 +1073,14 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0700-000005000000}" name="PivotTable5" cacheId="36" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0700-000005000000}" name="PivotTable5" cacheId="43" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Gemeinde" colHeaderCaption="Dossiertyp">
   <location ref="A3:C6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField dataField="1" showAll="0"/>
     <pivotField axis="axisCol" showAll="0">
-      <items count="8">
-        <item m="1" x="2"/>
-        <item m="1" x="5"/>
-        <item m="1" x="1"/>
-        <item m="1" x="6"/>
-        <item m="1" x="4"/>
+      <items count="2">
         <item x="0"/>
-        <item m="1" x="3"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -1108,14 +1088,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="9">
-        <item m="1" x="1"/>
-        <item m="1" x="2"/>
-        <item m="1" x="3"/>
-        <item m="1" x="4"/>
-        <item m="1" x="7"/>
-        <item m="1" x="5"/>
-        <item m="1" x="6"/>
+      <items count="2">
         <item x="0"/>
         <item t="default"/>
       </items>
@@ -1130,7 +1103,7 @@
   </rowFields>
   <rowItems count="2">
     <i>
-      <x v="7"/>
+      <x/>
     </i>
     <i t="grand">
       <x/>
@@ -1141,14 +1114,14 @@
   </colFields>
   <colItems count="2">
     <i>
-      <x v="5"/>
+      <x/>
     </i>
     <i t="grand">
       <x/>
     </i>
   </colItems>
   <dataFields count="1">
-    <dataField name="Anzahl von Dossier-Nr." fld="0" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Anzahl Dossiers" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -1438,131 +1411,131 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="13" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="D2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
+      <c r="D2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="D3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
+      <c r="D3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="D4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
+      <c r="D4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="D5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
+      <c r="D5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="D6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
+      <c r="D6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="D7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
+      <c r="D7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="D8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
+      <c r="D8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="D9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
+      <c r="D9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="D10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
+      <c r="D10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="D11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
+      <c r="D11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="D12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
+      <c r="D12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="D13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
+      <c r="D13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="D14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
+      <c r="D14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="D15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
+      <c r="D15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="D16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
+      <c r="D16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
     </row>
     <row r="17" spans="4:9">
-      <c r="D17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
+      <c r="D17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
     </row>
     <row r="18" spans="4:9">
-      <c r="D18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
+      <c r="D18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
     </row>
     <row r="19" spans="4:9">
-      <c r="D19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
+      <c r="D19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
     </row>
     <row r="20" spans="4:9">
-      <c r="D20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
+      <c r="D20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1573,6 +1546,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="17.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="s">
@@ -1584,54 +1560,54 @@
         <v>11</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="5">
         <f>COUNTIF(Data!G:G,"&lt;=30")</f>
         <v>0</v>
       </c>
-      <c r="C4" s="17" t="e">
+      <c r="C4" s="15" t="e">
         <f>COUNTIF(Data!G:G,"&lt;=30") / B7</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="6">
         <f>COUNTIFS(Data!G:G,"&gt;30",Data!G:G,"&lt;=60")</f>
         <v>0</v>
       </c>
-      <c r="C5" s="18" t="e">
+      <c r="C5" s="16" t="e">
         <f>COUNTIFS(Data!G:G,"&gt;30",Data!G:G,"&lt;=60") / B7</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="7">
         <f>COUNTIF(Data!G:G,"&gt;60")</f>
         <v>0</v>
       </c>
-      <c r="C6" s="19" t="e">
+      <c r="C6" s="17" t="e">
         <f>COUNTIF(Data!G:G,"&gt;60") / B7</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="8">
         <f>SUM(B4:B6)</f>
@@ -1646,37 +1622,40 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="10" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="15"/>
-    </row>
-    <row r="5" spans="1:2">
+      <c r="B4" s="20"/>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="15"/>
+      <c r="B5" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1685,37 +1664,40 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="10" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="12"/>
-    </row>
-    <row r="5" spans="1:2">
+      <c r="B4" s="19"/>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="B5" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1725,121 +1707,158 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.28515625" customWidth="1"/>
+    <col min="13" max="13" width="16.5703125" customWidth="1"/>
+    <col min="14" max="14" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="33" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="B3" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="9" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="G5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="12" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="13" t="e">
+        <v>31</v>
+      </c>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="G6" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="12" t="e">
         <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:8" ht="19.5" customHeight="1">
+      <c r="A1" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="H2" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="9" t="s">
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-    </row>
-    <row r="6" spans="1:3">
+        <v>17</v>
+      </c>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
+        <v>18</v>
+      </c>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1848,15 +1867,14 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -1890,43 +1908,46 @@
     <col min="39" max="39" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="9" t="s">
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-    </row>
-    <row r="6" spans="1:3">
+        <v>17</v>
+      </c>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
+        <v>18</v>
+      </c>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/django/camac/statistics/config/kt_ag/dossiers_service-afb.xlsx
+++ b/django/camac/statistics/config/kt_ag/dossiers_service-afb.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0353095-DDBF-48F9-AC27-E2412DC0E425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BED28D3-4ACF-4FFE-94F0-DB1B3160F049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="20565" tabRatio="887" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1290" yWindow="1620" windowWidth="20010" windowHeight="12885" tabRatio="887" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="43" r:id="rId8"/>
+    <pivotCache cacheId="21" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -131,9 +131,6 @@
     <t>Anzahl Dossiers nach Dossiertyp pro Zuständige Person</t>
   </si>
   <si>
-    <t>Anzahl fristgerechte erledigte Dossiers pro Zuständige Person</t>
-  </si>
-  <si>
     <t>Frist erreicht</t>
   </si>
   <si>
@@ -143,7 +140,10 @@
     <t>Anteil Dossiers</t>
   </si>
   <si>
-    <t>Anzhal Gesuche nach Dossiertyp pro Gemeinde</t>
+    <t>Anzahl Gesuche nach Dossiertyp pro Gemeinde</t>
+  </si>
+  <si>
+    <t>Anzahl fristgerechte (60 Tage) erledigte Dossiers pro Zuständige Person</t>
   </si>
 </sst>
 </file>
@@ -262,7 +262,7 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="14"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -435,9 +435,9 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="21">
     <cellStyle name="Accent" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
@@ -462,13 +462,7 @@
     <cellStyle name="Text" xfId="19" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
     <cellStyle name="Warning" xfId="20" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
@@ -489,7 +483,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Stoppe Tilo  Extern" refreshedDate="46121.734699884262" missingItemsLimit="0" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="20" xr:uid="{00000000-000A-0000-FFFF-FFFF50000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Stoppe Tilo  Extern" refreshedDate="46136.43192800926" missingItemsLimit="0" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="20" xr:uid="{00000000-000A-0000-FFFF-FFFF50000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:J1048576" sheet="Data"/>
   </cacheSource>
@@ -787,8 +781,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000001000000}" name="PivotTable3" cacheId="43" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" grandTotalCaption="Total Anzahl Dossiers" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person">
-  <location ref="A3:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000001000000}" name="PivotTable3" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" grandTotalCaption="Total Anzahl Dossiers" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person">
+  <location ref="A5:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
@@ -833,8 +827,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0400-000002000000}" name="PivotTable1" cacheId="43" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person">
-  <location ref="A3:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0400-000002000000}" name="PivotTable1" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person">
+  <location ref="A5:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -870,14 +864,14 @@
     <dataField name="Mittelwert von Durchlaufzeit in Tage" fld="6" subtotal="average" baseField="0" baseItem="0" numFmtId="1"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="3">
+    <format dxfId="1">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="2">
+    <format dxfId="0">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -897,8 +891,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B456AD4D-9646-4CC1-84EE-A09565AD0DDF}" name="PivotTable1" cacheId="43" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Frist erreicht">
-  <location ref="G3:H6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B456AD4D-9646-4CC1-84EE-A09565AD0DDF}" name="PivotTable1" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Frist erreicht">
+  <location ref="G5:H8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
@@ -956,8 +950,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-000003000000}" name="PivotTable2" cacheId="43" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" grandTotalCaption="Total" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Frist erreicht">
-  <location ref="A3:C6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-000003000000}" name="PivotTable2" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" grandTotalCaption="Total" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Frist erreicht">
+  <location ref="A5:C8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
@@ -1015,8 +1009,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0600-000004000000}" name="PivotTable4" cacheId="43" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Dossiertyp">
-  <location ref="A3:C6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0600-000004000000}" name="PivotTable4" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Dossiertyp">
+  <location ref="A5:C8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField dataField="1" showAll="0"/>
     <pivotField axis="axisCol" showAll="0">
@@ -1074,8 +1068,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0700-000005000000}" name="PivotTable5" cacheId="43" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Gemeinde" colHeaderCaption="Dossiertyp">
-  <location ref="A3:C6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0700-000005000000}" name="PivotTable5" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Gemeinde" colHeaderCaption="Dossiertyp">
+  <location ref="A5:C8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField dataField="1" showAll="0"/>
     <pivotField axis="axisCol" showAll="0">
@@ -1544,7 +1538,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="17.42578125" customWidth="1"/>
@@ -1555,65 +1549,65 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
+    <row r="5" spans="1:3">
+      <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="4" t="s">
+    <row r="6" spans="1:3">
+      <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B6" s="5">
         <f>COUNTIF(Data!G:G,"&lt;=30")</f>
         <v>0</v>
       </c>
-      <c r="C4" s="15" t="e">
-        <f>COUNTIF(Data!G:G,"&lt;=30") / B7</f>
+      <c r="C6" s="15" t="e">
+        <f>COUNTIF(Data!G:G,"&lt;=30") / B9</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B7" s="6">
         <f>COUNTIFS(Data!G:G,"&gt;30",Data!G:G,"&lt;=60")</f>
         <v>0</v>
       </c>
-      <c r="C5" s="16" t="e">
-        <f>COUNTIFS(Data!G:G,"&gt;30",Data!G:G,"&lt;=60") / B7</f>
+      <c r="C7" s="16" t="e">
+        <f>COUNTIFS(Data!G:G,"&gt;30",Data!G:G,"&lt;=60") / B9</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B8" s="7">
         <f>COUNTIF(Data!G:G,"&gt;60")</f>
         <v>0</v>
       </c>
-      <c r="C6" s="17" t="e">
-        <f>COUNTIF(Data!G:G,"&gt;60") / B7</f>
+      <c r="C8" s="17" t="e">
+        <f>COUNTIF(Data!G:G,"&gt;60") / B9</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
+    <row r="9" spans="1:3">
+      <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="8">
-        <f>SUM(B4:B6)</f>
+      <c r="B9" s="8">
+        <f>SUM(B6:B8)</f>
         <v>0</v>
       </c>
-      <c r="C7" s="8"/>
+      <c r="C9" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1622,40 +1616,40 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:5" ht="18.75">
+      <c r="A1" s="20" t="s">
         <v>23</v>
       </c>
       <c r="E1" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="9" t="s">
+    <row r="5" spans="1:5">
+      <c r="A5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="10" t="s">
+    <row r="6" spans="1:5">
+      <c r="A6" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="20"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="10" t="s">
+      <c r="B6" s="19"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="20"/>
+      <c r="B7" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1664,40 +1658,40 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:5" ht="18.75">
+      <c r="A1" s="20" t="s">
         <v>25</v>
       </c>
       <c r="E1" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="9" t="s">
+    <row r="5" spans="1:5">
+      <c r="A5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="10" t="s">
+    <row r="6" spans="1:5">
+      <c r="A6" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="19"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="10" t="s">
+      <c r="B6" s="18"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="19"/>
+      <c r="B7" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1707,18 +1701,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.28515625" customWidth="1"/>
     <col min="13" max="13" width="16.5703125" customWidth="1"/>
     <col min="14" max="14" width="21.42578125" bestFit="1" customWidth="1"/>
@@ -1729,68 +1724,68 @@
     <col min="34" max="35" width="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="18" t="s">
-        <v>29</v>
+    <row r="1" spans="1:10" ht="18.75">
+      <c r="A1" s="20" t="s">
+        <v>33</v>
       </c>
       <c r="J1" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="9" t="s">
+    <row r="5" spans="1:10">
+      <c r="A5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" s="9" t="s">
+      <c r="G6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="G7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="12" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="10" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="G5" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="12" t="e">
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="G6" s="10" t="s">
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="G8" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="12" t="e">
+      <c r="H8" s="12" t="e">
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -1802,20 +1797,21 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="19.5" customHeight="1">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>28</v>
       </c>
       <c r="H1" s="11" t="s">
@@ -1827,38 +1823,38 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="9" t="s">
+    <row r="5" spans="1:8">
+      <c r="A5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B5" s="9" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="9" t="s">
+    <row r="6" spans="1:8">
+      <c r="A6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B6" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="10" t="s">
+    <row r="7" spans="1:8">
+      <c r="A7" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="10" t="s">
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1867,14 +1863,15 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -1908,46 +1905,46 @@
     <col min="39" max="39" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" t="s">
-        <v>33</v>
+    <row r="1" spans="1:8" ht="18.75">
+      <c r="A1" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H1" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="9" t="s">
+    <row r="5" spans="1:8">
+      <c r="A5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B5" s="9" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="9" t="s">
+    <row r="6" spans="1:8">
+      <c r="A6" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B6" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="10" t="s">
+    <row r="7" spans="1:8">
+      <c r="A7" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="10" t="s">
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1955,26 +1952,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e238f3b-cf1c-4dc8-b1c3-14677632393c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb274a4b-4ecf-4ae2-a446-66548455045d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100D7FFFCF5F95BC94D9B7DF34B9D0CF76C" ma:contentTypeVersion="15" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="a8184ac6384f947bbc55bc4d9e1749d1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5e238f3b-cf1c-4dc8-b1c3-14677632393c" xmlns:ns3="a7360a35-2516-4210-888a-7cc8dd0a384d" xmlns:ns4="fb274a4b-4ecf-4ae2-a446-66548455045d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6dc33f40212c2dffa236803017f7661f" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="5e238f3b-cf1c-4dc8-b1c3-14677632393c"/>
@@ -2214,26 +2191,27 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e238f3b-cf1c-4dc8-b1c3-14677632393c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb274a4b-4ecf-4ae2-a446-66548455045d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1A7AABA-E440-4E84-AE0E-63CC059A281B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="5e238f3b-cf1c-4dc8-b1c3-14677632393c"/>
-    <ds:schemaRef ds:uri="fb274a4b-4ecf-4ae2-a446-66548455045d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF6C39F8-99B7-40C5-A3B9-C604A6AA2C4F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4DBF618-8A70-4A9F-99AC-8D5F60EB2F37}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2251,4 +2229,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF6C39F8-99B7-40C5-A3B9-C604A6AA2C4F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1A7AABA-E440-4E84-AE0E-63CC059A281B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5e238f3b-cf1c-4dc8-b1c3-14677632393c"/>
+    <ds:schemaRef ds:uri="fb274a4b-4ecf-4ae2-a446-66548455045d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/django/camac/statistics/config/kt_ag/dossiers_service-afb.xlsx
+++ b/django/camac/statistics/config/kt_ag/dossiers_service-afb.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BED28D3-4ACF-4FFE-94F0-DB1B3160F049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4B555FC-DF1E-44AE-9F37-529AA51DF187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1290" yWindow="1620" windowWidth="20010" windowHeight="12885" tabRatio="887" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="33105" windowHeight="17610" tabRatio="887" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="21" r:id="rId8"/>
+    <pivotCache cacheId="23" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -83,9 +83,6 @@
     <t>&lt;= 30 Tage</t>
   </si>
   <si>
-    <t>31 - 60 Tage</t>
-  </si>
-  <si>
     <t>&gt; 60 Tage</t>
   </si>
   <si>
@@ -144,6 +141,9 @@
   </si>
   <si>
     <t>Anzahl fristgerechte (60 Tage) erledigte Dossiers pro Zuständige Person</t>
+  </si>
+  <si>
+    <t>&lt;= 60 Tage</t>
   </si>
 </sst>
 </file>
@@ -436,8 +436,8 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="21">
     <cellStyle name="Accent" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
@@ -462,7 +462,13 @@
     <cellStyle name="Text" xfId="19" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
     <cellStyle name="Warning" xfId="20" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
@@ -483,7 +489,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Stoppe Tilo  Extern" refreshedDate="46136.43192800926" missingItemsLimit="0" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="20" xr:uid="{00000000-000A-0000-FFFF-FFFF50000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Stoppe Tilo  Extern" refreshedDate="46146.443703240744" missingItemsLimit="0" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="20" xr:uid="{00000000-000A-0000-FFFF-FFFF50000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:J1048576" sheet="Data"/>
   </cacheSource>
@@ -781,7 +787,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000001000000}" name="PivotTable3" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" grandTotalCaption="Total Anzahl Dossiers" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000001000000}" name="PivotTable3" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" grandTotalCaption="Total Anzahl Dossiers" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person">
   <location ref="A5:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField dataField="1" showAll="0"/>
@@ -827,7 +833,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0400-000002000000}" name="PivotTable1" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0400-000002000000}" name="PivotTable1" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person">
   <location ref="A5:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -864,14 +870,14 @@
     <dataField name="Mittelwert von Durchlaufzeit in Tage" fld="6" subtotal="average" baseField="0" baseItem="0" numFmtId="1"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="1">
+    <format dxfId="3">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="0">
+    <format dxfId="2">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -891,7 +897,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B456AD4D-9646-4CC1-84EE-A09565AD0DDF}" name="PivotTable1" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Frist erreicht">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B456AD4D-9646-4CC1-84EE-A09565AD0DDF}" name="PivotTable1" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Frist erreicht">
   <location ref="G5:H8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField dataField="1" showAll="0"/>
@@ -950,7 +956,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-000003000000}" name="PivotTable2" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" grandTotalCaption="Total" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Frist erreicht">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-000003000000}" name="PivotTable2" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" grandTotalCaption="Total" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Frist erreicht">
   <location ref="A5:C8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField dataField="1" showAll="0"/>
@@ -1009,7 +1015,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0600-000004000000}" name="PivotTable4" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Dossiertyp">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0600-000004000000}" name="PivotTable4" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Dossiertyp">
   <location ref="A5:C8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField dataField="1" showAll="0"/>
@@ -1068,7 +1074,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0700-000005000000}" name="PivotTable5" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Gemeinde" colHeaderCaption="Dossiertyp">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0700-000005000000}" name="PivotTable5" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Gemeinde" colHeaderCaption="Dossiertyp">
   <location ref="A5:C8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField dataField="1" showAll="0"/>
@@ -1554,10 +1560,10 @@
         <v>11</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1575,20 +1581,20 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B7" s="6">
-        <f>COUNTIFS(Data!G:G,"&gt;30",Data!G:G,"&lt;=60")</f>
+        <f>COUNTIF(Data!G:G,"&lt;=60")</f>
         <v>0</v>
       </c>
       <c r="C7" s="16" t="e">
-        <f>COUNTIFS(Data!G:G,"&gt;30",Data!G:G,"&lt;=60") / B9</f>
+        <f>COUNTIF(Data!G:G,"&lt;=60") / B9</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="7">
         <f>COUNTIF(Data!G:G,"&gt;60")</f>
@@ -1601,10 +1607,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="8">
-        <f>SUM(B6:B8)</f>
+        <f>COUNTIF(Data!G:G,"&gt;=0")</f>
         <v>0</v>
       </c>
       <c r="C9" s="8"/>
@@ -1624,32 +1630,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18.75">
-      <c r="A1" s="20" t="s">
-        <v>23</v>
+      <c r="A1" s="19" t="s">
+        <v>22</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="19"/>
+        <v>16</v>
+      </c>
+      <c r="B6" s="20"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="19"/>
+        <v>21</v>
+      </c>
+      <c r="B7" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1666,30 +1672,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18.75">
-      <c r="A1" s="20" t="s">
-        <v>25</v>
+      <c r="A1" s="19" t="s">
+        <v>24</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" s="18"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" s="18"/>
     </row>
@@ -1725,52 +1731,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.75">
-      <c r="A1" s="20" t="s">
-        <v>33</v>
+      <c r="A1" s="19" t="s">
+        <v>32</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
+        <v>16</v>
+      </c>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
       <c r="G7" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H7" s="12" t="e">
         <v>#DIV/0!</v>
@@ -1778,12 +1784,12 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
+        <v>29</v>
+      </c>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
       <c r="G8" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H8" s="12" t="e">
         <v>#DIV/0!</v>
@@ -1811,50 +1817,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="19.5" customHeight="1">
-      <c r="A1" s="20" t="s">
-        <v>28</v>
+      <c r="A1" s="19" t="s">
+        <v>27</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="H2" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
         <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
+        <v>16</v>
+      </c>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
+        <v>17</v>
+      </c>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1907,18 +1913,18 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.75">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1926,25 +1932,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
         <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
+        <v>16</v>
+      </c>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
+        <v>17</v>
+      </c>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/django/camac/statistics/config/kt_ag/dossiers_service-afb.xlsx
+++ b/django/camac/statistics/config/kt_ag/dossiers_service-afb.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4B555FC-DF1E-44AE-9F37-529AA51DF187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B86B443-A842-421A-AE6A-FCB91CDFAA9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="33105" windowHeight="17610" tabRatio="887" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="23" r:id="rId8"/>
+    <pivotCache cacheId="7" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="35">
   <si>
     <t>Dossier-Nr.</t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>&lt;= 60 Tage</t>
+  </si>
+  <si>
+    <t>Fristgerecht: 0 = nicht fristgerecht, 1 = fristgerecht</t>
   </si>
 </sst>
 </file>
@@ -489,7 +492,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Stoppe Tilo  Extern" refreshedDate="46146.443703240744" missingItemsLimit="0" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="20" xr:uid="{00000000-000A-0000-FFFF-FFFF50000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Stoppe Tilo  Extern" refreshedDate="46146.649539004633" missingItemsLimit="0" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="20" xr:uid="{00000000-000A-0000-FFFF-FFFF50000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:J1048576" sheet="Data"/>
   </cacheSource>
@@ -787,7 +790,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000001000000}" name="PivotTable3" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" grandTotalCaption="Total Anzahl Dossiers" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000001000000}" name="PivotTable3" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" grandTotalCaption="Total Anzahl Dossiers" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person">
   <location ref="A5:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField dataField="1" showAll="0"/>
@@ -833,7 +836,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0400-000002000000}" name="PivotTable1" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0400-000002000000}" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person">
   <location ref="A5:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -897,7 +900,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B456AD4D-9646-4CC1-84EE-A09565AD0DDF}" name="PivotTable1" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Frist erreicht">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B456AD4D-9646-4CC1-84EE-A09565AD0DDF}" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Frist erreicht">
   <location ref="G5:H8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField dataField="1" showAll="0"/>
@@ -956,7 +959,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-000003000000}" name="PivotTable2" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" grandTotalCaption="Total" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Frist erreicht">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-000003000000}" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" grandTotalCaption="Total" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Frist erreicht">
   <location ref="A5:C8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField dataField="1" showAll="0"/>
@@ -1015,7 +1018,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0600-000004000000}" name="PivotTable4" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Dossiertyp">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0600-000004000000}" name="PivotTable4" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Dossiertyp">
   <location ref="A5:C8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField dataField="1" showAll="0"/>
@@ -1074,7 +1077,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0700-000005000000}" name="PivotTable5" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Gemeinde" colHeaderCaption="Dossiertyp">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0700-000005000000}" name="PivotTable5" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Gemeinde" colHeaderCaption="Dossiertyp">
   <location ref="A5:C8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField dataField="1" showAll="0"/>
@@ -1738,6 +1741,11 @@
         <v>15</v>
       </c>
     </row>
+    <row r="2" spans="1:10">
+      <c r="J2" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
     <row r="5" spans="1:10">
       <c r="A5" s="9" t="s">
         <v>19</v>
@@ -1828,6 +1836,9 @@
       <c r="H2" s="11" t="s">
         <v>15</v>
       </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="H3" s="11"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="9" t="s">
@@ -1919,6 +1930,9 @@
         <v>15</v>
       </c>
     </row>
+    <row r="2" spans="1:8">
+      <c r="H2" s="11"/>
+    </row>
     <row r="5" spans="1:8">
       <c r="A5" s="9" t="s">
         <v>19</v>
@@ -1958,6 +1972,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100D7FFFCF5F95BC94D9B7DF34B9D0CF76C" ma:contentTypeVersion="15" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="a8184ac6384f947bbc55bc4d9e1749d1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5e238f3b-cf1c-4dc8-b1c3-14677632393c" xmlns:ns3="a7360a35-2516-4210-888a-7cc8dd0a384d" xmlns:ns4="fb274a4b-4ecf-4ae2-a446-66548455045d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6dc33f40212c2dffa236803017f7661f" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="5e238f3b-cf1c-4dc8-b1c3-14677632393c"/>
@@ -2197,15 +2220,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2218,6 +2232,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF6C39F8-99B7-40C5-A3B9-C604A6AA2C4F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4DBF618-8A70-4A9F-99AC-8D5F60EB2F37}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2237,14 +2259,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF6C39F8-99B7-40C5-A3B9-C604A6AA2C4F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1A7AABA-E440-4E84-AE0E-63CC059A281B}">
   <ds:schemaRefs>
